--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,132 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115042437</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Karltorp (Karltorp), Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>528885</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6580427</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Trummar</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,6 +1061,127 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122936355</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56821</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Karltorp, Karltorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528968</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6580074</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg, Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1182,6 +1182,268 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123270234</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57394</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>S Karltorp, S Karltorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>529034</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6580012</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kretsar långsamt mot SO</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123269057</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57394</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>S Karltorp, S Karltorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>529034</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6580011</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flyger in från ONO och kretsar 5 min rakt över min position, drar på hög höjd mot SO.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>122767418</v>
       </c>
       <c r="B4" t="n">
-        <v>57394</v>
+        <v>57397</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>122936355</v>
       </c>
       <c r="B5" t="n">
-        <v>56821</v>
+        <v>56824</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123270234</v>
+        <v>123269057</v>
       </c>
       <c r="B6" t="n">
-        <v>57394</v>
+        <v>57397</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1241,7 +1241,7 @@
         <v>529034</v>
       </c>
       <c r="R6" t="n">
-        <v>6580012</v>
+        <v>6580011</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Kretsar långsamt mot SO</t>
+          <t>Flyger in från ONO och kretsar 5 min rakt över min position, drar på hög höjd mot SO.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123269057</v>
+        <v>123270234</v>
       </c>
       <c r="B7" t="n">
-        <v>57394</v>
+        <v>57397</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1372,7 +1372,7 @@
         <v>529034</v>
       </c>
       <c r="R7" t="n">
-        <v>6580011</v>
+        <v>6580012</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flyger in från ONO och kretsar 5 min rakt över min position, drar på hög höjd mot SO.</t>
+          <t>Kretsar långsamt mot SO</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -1184,7 +1184,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123269057</v>
+        <v>123270234</v>
       </c>
       <c r="B6" t="n">
         <v>57397</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1241,7 +1241,7 @@
         <v>529034</v>
       </c>
       <c r="R6" t="n">
-        <v>6580011</v>
+        <v>6580012</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flyger in från ONO och kretsar 5 min rakt över min position, drar på hög höjd mot SO.</t>
+          <t>Kretsar långsamt mot SO</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,7 +1315,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123270234</v>
+        <v>123269057</v>
       </c>
       <c r="B7" t="n">
         <v>57397</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1372,7 +1372,7 @@
         <v>529034</v>
       </c>
       <c r="R7" t="n">
-        <v>6580012</v>
+        <v>6580011</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Kretsar långsamt mot SO</t>
+          <t>Flyger in från ONO och kretsar 5 min rakt över min position, drar på hög höjd mot SO.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>122936355</v>
       </c>
       <c r="B5" t="n">
-        <v>56824</v>
+        <v>56830</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123270234</v>
+        <v>123269057</v>
       </c>
       <c r="B6" t="n">
-        <v>57397</v>
+        <v>57403</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1241,7 +1241,7 @@
         <v>529034</v>
       </c>
       <c r="R6" t="n">
-        <v>6580012</v>
+        <v>6580011</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Kretsar långsamt mot SO</t>
+          <t>Flyger in från ONO och kretsar 5 min rakt över min position, drar på hög höjd mot SO.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123269057</v>
+        <v>123270234</v>
       </c>
       <c r="B7" t="n">
-        <v>57397</v>
+        <v>57403</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1372,7 +1372,7 @@
         <v>529034</v>
       </c>
       <c r="R7" t="n">
-        <v>6580011</v>
+        <v>6580012</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flyger in från ONO och kretsar 5 min rakt över min position, drar på hög höjd mot SO.</t>
+          <t>Kretsar långsamt mot SO</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -1184,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123269057</v>
+        <v>123270234</v>
       </c>
       <c r="B6" t="n">
-        <v>57403</v>
+        <v>57406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1241,7 +1241,7 @@
         <v>529034</v>
       </c>
       <c r="R6" t="n">
-        <v>6580011</v>
+        <v>6580012</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flyger in från ONO och kretsar 5 min rakt över min position, drar på hög höjd mot SO.</t>
+          <t>Kretsar långsamt mot SO</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123270234</v>
+        <v>123269057</v>
       </c>
       <c r="B7" t="n">
-        <v>57403</v>
+        <v>57406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1372,7 +1372,7 @@
         <v>529034</v>
       </c>
       <c r="R7" t="n">
-        <v>6580012</v>
+        <v>6580011</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Kretsar långsamt mot SO</t>
+          <t>Flyger in från ONO och kretsar 5 min rakt över min position, drar på hög höjd mot SO.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -1187,7 +1187,7 @@
         <v>123270234</v>
       </c>
       <c r="B6" t="n">
-        <v>57406</v>
+        <v>57407</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>123269057</v>
       </c>
       <c r="B7" t="n">
-        <v>57406</v>
+        <v>57407</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -1184,7 +1184,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123270234</v>
+        <v>123269057</v>
       </c>
       <c r="B6" t="n">
         <v>57407</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1241,7 +1241,7 @@
         <v>529034</v>
       </c>
       <c r="R6" t="n">
-        <v>6580012</v>
+        <v>6580011</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Kretsar långsamt mot SO</t>
+          <t>Flyger in från ONO och kretsar 5 min rakt över min position, drar på hög höjd mot SO.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,7 +1315,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123269057</v>
+        <v>123270234</v>
       </c>
       <c r="B7" t="n">
         <v>57407</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1372,7 +1372,7 @@
         <v>529034</v>
       </c>
       <c r="R7" t="n">
-        <v>6580011</v>
+        <v>6580012</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flyger in från ONO och kretsar 5 min rakt över min position, drar på hög höjd mot SO.</t>
+          <t>Kretsar långsamt mot SO</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1444,6 +1444,484 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126040725</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57824</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mellby, Mellby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>529049</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6579957</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126040913</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58154</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mellby, Mellby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>529057</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6579972</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126058976</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hygge NV Mellby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>529059</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6579989</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg, Roine Magnusson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126040810</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57473</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mellby, Mellby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>529049</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6579957</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>126040725</v>
       </c>
       <c r="B8" t="n">
-        <v>57824</v>
+        <v>57825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>126040913</v>
       </c>
       <c r="B9" t="n">
-        <v>58154</v>
+        <v>58155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126058976</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Carlberg, Roine Magnusson</t>
+          <t>Roine Magnusson, Tomas Carlberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1811,7 +1811,7 @@
         <v>126040810</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -1801,7 +1801,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roine Magnusson, Tomas Carlberg</t>
+          <t>Tomas Carlberg, Roine Magnusson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>126040725</v>
       </c>
       <c r="B8" t="n">
-        <v>57825</v>
+        <v>57829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>126040913</v>
       </c>
       <c r="B9" t="n">
-        <v>58155</v>
+        <v>58159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126058976</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57742</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>126040810</v>
       </c>
       <c r="B11" t="n">
-        <v>57474</v>
+        <v>57478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1922,6 +1922,465 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126332339</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57742</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hygge NV Mellby, Hygge NV Mellby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>529028</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6580012</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg, Roine Magnusson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126362620</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58159</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hygge NV Mellby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>529059</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6579989</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Par med &gt;2 ungar</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg, Roine Magnusson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126363196</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57829</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hygge NV Mellby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>529059</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6579989</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg, Roine Magnusson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126363192</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57068</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hygge NV Mellby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>529059</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6579989</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg, Roine Magnusson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31234-2023 artfynd.xlsx
+++ b/artfynd/A 31234-2023 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>126040725</v>
       </c>
       <c r="B8" t="n">
-        <v>57829</v>
+        <v>57830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>126040913</v>
       </c>
       <c r="B9" t="n">
-        <v>58159</v>
+        <v>58162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126058976</v>
       </c>
       <c r="B10" t="n">
-        <v>57742</v>
+        <v>57743</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>126040810</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57479</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>126332339</v>
       </c>
       <c r="B12" t="n">
-        <v>57742</v>
+        <v>57743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>126362620</v>
       </c>
       <c r="B13" t="n">
-        <v>58159</v>
+        <v>58162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>126363196</v>
       </c>
       <c r="B14" t="n">
-        <v>57829</v>
+        <v>57830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>126363192</v>
       </c>
       <c r="B15" t="n">
-        <v>57068</v>
+        <v>57069</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
